--- a/diseases/d018/2005-2009.xlsx
+++ b/diseases/d018/2005-2009.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>24</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.05015501661761088</v>
       </c>
@@ -913,9 +910,6 @@
       <c r="O3" t="n">
         <v>7</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.01462854651346984</v>
       </c>
@@ -1061,9 +1055,6 @@
       <c r="O4" t="n">
         <v>10</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.0208979235906712</v>
       </c>
@@ -1209,9 +1200,6 @@
       <c r="O5" t="n">
         <v>10</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.0208979235906712</v>
       </c>
@@ -1357,9 +1345,6 @@
       <c r="O6" t="n">
         <v>11</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.02298771594973832</v>
       </c>
@@ -1505,9 +1490,6 @@
       <c r="O7" t="n">
         <v>11</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.02298771594973832</v>
       </c>
@@ -1653,9 +1635,6 @@
       <c r="O8" t="n">
         <v>7</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.01462854651346984</v>
       </c>
@@ -1801,9 +1780,6 @@
       <c r="O9" t="n">
         <v>7</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.01462854651346984</v>
       </c>
@@ -1949,9 +1925,6 @@
       <c r="O10" t="n">
         <v>21</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.04388563954040952</v>
       </c>
@@ -2097,9 +2070,6 @@
       <c r="O11" t="n">
         <v>86</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.1797221428797723</v>
       </c>
@@ -2245,9 +2215,6 @@
       <c r="O12" t="n">
         <v>155</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.3239178156554036</v>
       </c>
@@ -2393,9 +2360,6 @@
       <c r="O13" t="n">
         <v>72</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.1504650498528326</v>
       </c>
@@ -2541,9 +2505,6 @@
       <c r="O14" t="n">
         <v>24</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.04999321185920225</v>
       </c>
@@ -2689,9 +2650,6 @@
       <c r="O15" t="n">
         <v>10</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.02083050494133427</v>
       </c>
@@ -2837,9 +2795,6 @@
       <c r="O16" t="n">
         <v>9</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.01874745444720084</v>
       </c>
@@ -2985,9 +2940,6 @@
       <c r="O17" t="n">
         <v>9</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.01874745444720084</v>
       </c>
@@ -3133,9 +3085,6 @@
       <c r="O18" t="n">
         <v>13</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.02707965642373455</v>
       </c>
@@ -3281,9 +3230,6 @@
       <c r="O19" t="n">
         <v>15</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.0312457574120014</v>
       </c>
@@ -3429,9 +3375,6 @@
       <c r="O20" t="n">
         <v>13</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.02707965642373455</v>
       </c>
@@ -3577,9 +3520,6 @@
       <c r="O21" t="n">
         <v>11</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.02291355543546769</v>
       </c>
@@ -3725,9 +3665,6 @@
       <c r="O22" t="n">
         <v>31</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.06457456531813623</v>
       </c>
@@ -3873,9 +3810,6 @@
       <c r="O23" t="n">
         <v>95</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.1978897969426756</v>
       </c>
@@ -4021,9 +3955,6 @@
       <c r="O24" t="n">
         <v>128</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.2666304632490786</v>
       </c>
@@ -4169,9 +4100,6 @@
       <c r="O25" t="n">
         <v>64</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.1333152316245393</v>
       </c>
@@ -4317,9 +4245,6 @@
       <c r="O26" t="n">
         <v>21</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.04358825262136378</v>
       </c>
@@ -4465,9 +4390,6 @@
       <c r="O27" t="n">
         <v>11</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.02283194184928579</v>
       </c>
@@ -4613,9 +4535,6 @@
       <c r="O28" t="n">
         <v>7</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.0145294175404546</v>
       </c>
@@ -4761,9 +4680,6 @@
       <c r="O29" t="n">
         <v>8</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.01660504861766239</v>
       </c>
@@ -4909,9 +4825,6 @@
       <c r="O30" t="n">
         <v>14</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.02905883508090919</v>
       </c>
@@ -5057,9 +4970,6 @@
       <c r="O31" t="n">
         <v>6</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.01245378646324679</v>
       </c>
@@ -5205,9 +5115,6 @@
       <c r="O32" t="n">
         <v>14</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.02905883508090919</v>
       </c>
@@ -5353,9 +5260,6 @@
       <c r="O33" t="n">
         <v>12</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.02490757292649359</v>
       </c>
@@ -5501,9 +5405,6 @@
       <c r="O34" t="n">
         <v>9</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.01868067969487019</v>
       </c>
@@ -5649,9 +5550,6 @@
       <c r="O35" t="n">
         <v>73</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.1515210686361693</v>
       </c>
@@ -5797,9 +5695,6 @@
       <c r="O36" t="n">
         <v>211</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.4379581572908456</v>
       </c>
@@ -5945,9 +5840,6 @@
       <c r="O37" t="n">
         <v>64</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.1328403889412992</v>
       </c>
@@ -6093,9 +5985,6 @@
       <c r="O38" t="n">
         <v>27</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.05583531460811271</v>
       </c>
@@ -6241,9 +6130,6 @@
       <c r="O39" t="n">
         <v>8</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.01654379692092229</v>
       </c>
@@ -6389,9 +6275,6 @@
       <c r="O40" t="n">
         <v>6</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.01240784769069171</v>
       </c>
@@ -6537,9 +6420,6 @@
       <c r="O41" t="n">
         <v>5</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.01033987307557643</v>
       </c>
@@ -6685,9 +6565,6 @@
       <c r="O42" t="n">
         <v>10</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.02067974615115285</v>
       </c>
@@ -6833,9 +6710,6 @@
       <c r="O43" t="n">
         <v>13</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.02688366999649871</v>
       </c>
@@ -6981,9 +6855,6 @@
       <c r="O44" t="n">
         <v>10</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.02067974615115285</v>
       </c>
@@ -7129,9 +7000,6 @@
       <c r="O45" t="n">
         <v>11</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.02274772076626814</v>
       </c>
@@ -7277,9 +7145,6 @@
       <c r="O46" t="n">
         <v>17</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.03515556845695986</v>
       </c>
@@ -7425,9 +7290,6 @@
       <c r="O47" t="n">
         <v>80</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.1654379692092228</v>
       </c>
@@ -7573,9 +7435,6 @@
       <c r="O48" t="n">
         <v>130</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.2688366999649872</v>
       </c>
@@ -7721,9 +7580,6 @@
       <c r="O49" t="n">
         <v>58</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.1199425276766866</v>
       </c>
@@ -7869,9 +7725,6 @@
       <c r="O50" t="n">
         <v>15</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.03089809229307545</v>
       </c>
@@ -8017,9 +7870,6 @@
       <c r="O51" t="n">
         <v>6</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.01235923691723018</v>
       </c>
@@ -8165,9 +8015,6 @@
       <c r="O52" t="n">
         <v>9</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.01853885537584527</v>
       </c>
@@ -8313,9 +8160,6 @@
       <c r="O53" t="n">
         <v>11</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.022658601014922</v>
       </c>
@@ -8461,9 +8305,6 @@
       <c r="O54" t="n">
         <v>10</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.02059872819538363</v>
       </c>
@@ -8609,9 +8450,6 @@
       <c r="O55" t="n">
         <v>20</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.04119745639076727</v>
       </c>
@@ -8757,9 +8595,6 @@
       <c r="O56" t="n">
         <v>12</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.02471847383446036</v>
       </c>
@@ -8905,9 +8740,6 @@
       <c r="O57" t="n">
         <v>10</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.02059872819538363</v>
       </c>
@@ -9053,9 +8885,6 @@
       <c r="O58" t="n">
         <v>19</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.0391375835712289</v>
       </c>
@@ -9201,9 +9030,6 @@
       <c r="O59" t="n">
         <v>60</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.1235923691723018</v>
       </c>
@@ -9349,9 +9175,6 @@
       <c r="O60" t="n">
         <v>110</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.22658601014922</v>
       </c>
@@ -9496,9 +9319,6 @@
       </c>
       <c r="O61" t="n">
         <v>52</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0.1071133866159949</v>
